--- a/TestData/T2011_GiftLog_GiftRequestProcess_GiftSubmitted_GiftRequestDetailLayoutAndFields.xlsx
+++ b/TestData/T2011_GiftLog_GiftRequestProcess_GiftSubmitted_GiftRequestDetailLayoutAndFields.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\HL\SalesForce_Project\SalesForce_Project\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8E1EF67-313A-4F94-95B9-9C9B4172ADCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60B626CA-4BF2-445F-92AE-3D52AECA288C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GiftLog" sheetId="4" r:id="rId1"/>
@@ -67,9 +67,6 @@
     <t>ContactName</t>
   </si>
   <si>
-    <t>Test External</t>
-  </si>
-  <si>
     <t>CongratulationsMsg</t>
   </si>
   <si>
@@ -107,6 +104,9 @@
   </si>
   <si>
     <t>1</t>
+  </si>
+  <si>
+    <t>Giftlog Contact</t>
   </si>
 </sst>
 </file>
@@ -435,28 +435,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.109375" customWidth="1"/>
-    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>4</v>
@@ -465,7 +465,7 @@
         <v>5</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -483,30 +483,30 @@
         <v>1</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>22</v>
-      </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F2" t="s">
         <v>8</v>
@@ -515,22 +515,22 @@
         <v>10</v>
       </c>
       <c r="H2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="J2" t="s">
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -542,19 +542,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
